--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,3191 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131566310</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>419633</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7056685</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131566305</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75231</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7056648</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131566303</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79509</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419713</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7056649</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131566308</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92543</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>419698</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7056652</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131566325</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89206</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>510</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>419367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7056739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131566316</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80387</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>419586</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7056712</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131566311</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>419593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7056723</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131566321</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>419413</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7056727</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131566319</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79253</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>419473</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7056721</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131566317</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>419510</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7056746</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131566295</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83233</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>419674</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7056595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131566314</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>419597</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131566326</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80318</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>419407</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056625</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131566299</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83216</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>419733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056597</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131566297</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83099</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>419727</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056633</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131566312</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>419590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7056714</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131566302</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83238</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>419713</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056649</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>under rotben på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131566322</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78265</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>419409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7056725</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131566315</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>419594</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7056698</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131566293</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79253</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>419706</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7056590</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131566313</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>419603</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7056711</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131566307</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79253</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>419663</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7056675</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131566323</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92543</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>419357</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7056778</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131566304</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92543</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>419713</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7056649</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131566324</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>419354</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7056785</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131566301</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>419715</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7056651</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131566306</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>419655</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7056675</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131566294</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83238</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>419680</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7056589</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>under rotben på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131566318</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>419515</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7056725</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
         <v>131566310</v>
       </c>
       <c r="B3" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131566305</v>
       </c>
       <c r="B4" t="n">
-        <v>75231</v>
+        <v>75232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>131566303</v>
       </c>
       <c r="B5" t="n">
-        <v>79509</v>
+        <v>79510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>131566308</v>
       </c>
       <c r="B6" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>131566325</v>
       </c>
       <c r="B7" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131566316</v>
       </c>
       <c r="B8" t="n">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131566311</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>131566321</v>
       </c>
       <c r="B10" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131566319</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131566317</v>
       </c>
       <c r="B12" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>131566295</v>
       </c>
       <c r="B13" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>131566314</v>
       </c>
       <c r="B14" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>131566326</v>
       </c>
       <c r="B15" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131566299</v>
       </c>
       <c r="B16" t="n">
-        <v>83216</v>
+        <v>83217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>131566297</v>
       </c>
       <c r="B17" t="n">
-        <v>83099</v>
+        <v>83100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>131566312</v>
       </c>
       <c r="B18" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>131566302</v>
       </c>
       <c r="B19" t="n">
-        <v>83238</v>
+        <v>83239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131566322</v>
+        <v>131566315</v>
       </c>
       <c r="B20" t="n">
-        <v>78265</v>
+        <v>80359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419409</v>
+        <v>419594</v>
       </c>
       <c r="R20" t="n">
-        <v>7056725</v>
+        <v>7056698</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131566315</v>
+        <v>131566293</v>
       </c>
       <c r="B21" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419594</v>
+        <v>419706</v>
       </c>
       <c r="R21" t="n">
-        <v>7056698</v>
+        <v>7056590</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,21 +2882,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2913,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131566293</v>
+        <v>131566322</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>78266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,21 +2909,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2948,10 +2933,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419706</v>
+        <v>419409</v>
       </c>
       <c r="R22" t="n">
-        <v>7056590</v>
+        <v>7056725</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,7 +2968,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2993,7 +2978,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,6 +2989,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3023,7 +3023,7 @@
         <v>131566313</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>79335</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>131566307</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>131566323</v>
       </c>
       <c r="B25" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>131566304</v>
       </c>
       <c r="B26" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>131566324</v>
       </c>
       <c r="B27" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>131566301</v>
       </c>
       <c r="B28" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131566306</v>
       </c>
       <c r="B29" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>131566294</v>
       </c>
       <c r="B30" t="n">
-        <v>83238</v>
+        <v>83239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>131566318</v>
       </c>
       <c r="B31" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3991,6 +3991,6277 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131584340</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>418697</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7056879</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131584325</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>418928</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7056947</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131584322</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>419747</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7056615</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål ca 3,3 m upp i grantickerötad granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131584336</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>419047</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7056875</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131584555</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>419343</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7056648</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en ca 6 meter hög granhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131584568</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>418619</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7056987</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Betula</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131584561</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>419013</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7056860</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131584544</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80360</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>419333</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7056680</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131584565</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>418773</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7056981</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131584546</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80360</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>419073</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7056773</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131584339</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>418677</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7056893</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131584326</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>418619</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7056989</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Observerades hackandes på både gran och björk</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131584547</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80395</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>419307</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7056721</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131584550</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>419077</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7056784</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående levande grov gran.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131584541</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>418507</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7057041</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal grov gran.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131584350</v>
+      </c>
+      <c r="B47" t="n">
+        <v>89207</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>510</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>419731</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7056563</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131584562</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>418989</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7056899</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131584320</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>419749</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7056588</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131584571</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>418510</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7057043</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Växer här på en gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131584563</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>418925</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7056918</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131584328</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58051</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>419750</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7056612</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131584321</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>419741</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7056603</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131584567</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>418672</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7056939</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt på en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131584558</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>419228</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7056767</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131584323</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>419542</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7056682</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131584556</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>419342</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7056685</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131584569</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>418566</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7057014</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med garnlav på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131584334</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>419494</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7056656</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131584327</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>418610</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7056996</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131584560</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>419058</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7056809</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131584337</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>419005</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7056915</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131584324</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>419365</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7056680</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131584331</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92241</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>419500</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7056661</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131584335</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>419501</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7056663</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131584566</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>418673</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7056906</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131584543</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80388</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>419307</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7056720</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131584554</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>419395</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7056573</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131584542</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58051</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>418940</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7056963</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal bitvis flerskiktad och luckig granskog med murkna björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131584329</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57889</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>418697</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7056879</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131584333</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>419555</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7056651</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131584319</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>419476</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7056575</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131584553</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>419469</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7056553</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131584347</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>418505</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7057056</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131584338</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>418936</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7056928</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131584332</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>419747</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7056611</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131584314</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92544</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>419729</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7056657</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131584545</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80360</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>419306</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7056720</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131584559</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>419132</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7056815</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131584346</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>418537</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7057018</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131584315</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92544</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>419707</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7056665</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131584330</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92241</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>418867</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7056983</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131584317</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92544</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skalet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>419081</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7056790</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131584539</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>419098</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7056781</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131584557</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79254</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>419261</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7056756</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131584538</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57892</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>419244</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7056755</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående döende gran med full längd och 41 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -5779,10 +5779,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131584350</v>
+        <v>131584562</v>
       </c>
       <c r="B47" t="n">
-        <v>89207</v>
+        <v>79254</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5790,34 +5790,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419731</v>
+        <v>418989</v>
       </c>
       <c r="R47" t="n">
-        <v>7056563</v>
+        <v>7056899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5858,28 +5861,49 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131584562</v>
+        <v>131584350</v>
       </c>
       <c r="B48" t="n">
-        <v>79254</v>
+        <v>89207</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5887,37 +5911,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>418989</v>
+        <v>419731</v>
       </c>
       <c r="R48" t="n">
-        <v>7056899</v>
+        <v>7056563</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5958,39 +5979,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -9767,45 +9767,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131584317</v>
+        <v>131584539</v>
       </c>
       <c r="B83" t="n">
-        <v>92544</v>
+        <v>57892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419081</v>
+        <v>419098</v>
       </c>
       <c r="R83" t="n">
-        <v>7056790</v>
+        <v>7056781</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9840,6 +9848,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gammal gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9848,26 +9861,51 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131584539</v>
+        <v>131584557</v>
       </c>
       <c r="B84" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9875,31 +9913,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9907,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419098</v>
+        <v>419261</v>
       </c>
       <c r="R84" t="n">
-        <v>7056781</v>
+        <v>7056756</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9947,7 +9980,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9956,6 +9989,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9976,12 +10010,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9999,10 +10033,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131584557</v>
+        <v>131584538</v>
       </c>
       <c r="B85" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10010,26 +10044,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10037,10 +10076,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419261</v>
+        <v>419244</v>
       </c>
       <c r="R85" t="n">
-        <v>7056756</v>
+        <v>7056755</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10077,7 +10116,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en stående döende gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10086,7 +10125,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10107,12 +10145,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10130,53 +10168,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131584538</v>
+        <v>131584317</v>
       </c>
       <c r="B86" t="n">
-        <v>57892</v>
+        <v>92544</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419244</v>
+        <v>419081</v>
       </c>
       <c r="R86" t="n">
-        <v>7056755</v>
+        <v>7056790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10211,11 +10241,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående döende gran med full längd och 41 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10224,41 +10249,16 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,7 +812,7 @@
         <v>131566310</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>79419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131566305</v>
       </c>
       <c r="B4" t="n">
-        <v>75232</v>
+        <v>75238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566303</v>
+        <v>131566308</v>
       </c>
       <c r="B5" t="n">
-        <v>79510</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419713</v>
+        <v>419698</v>
       </c>
       <c r="R5" t="n">
-        <v>7056649</v>
+        <v>7056652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566308</v>
+        <v>131566303</v>
       </c>
       <c r="B6" t="n">
-        <v>92544</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419698</v>
+        <v>419713</v>
       </c>
       <c r="R6" t="n">
-        <v>7056652</v>
+        <v>7056649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
         <v>131566325</v>
       </c>
       <c r="B7" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131566316</v>
       </c>
       <c r="B8" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131566311</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>131566321</v>
       </c>
       <c r="B10" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131566319</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131566317</v>
       </c>
       <c r="B12" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131566295</v>
+        <v>131566314</v>
       </c>
       <c r="B13" t="n">
-        <v>83234</v>
+        <v>79419</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419674</v>
+        <v>419597</v>
       </c>
       <c r="R13" t="n">
-        <v>7056595</v>
+        <v>7056713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131566314</v>
+        <v>131566295</v>
       </c>
       <c r="B14" t="n">
-        <v>79413</v>
+        <v>83240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419597</v>
+        <v>419674</v>
       </c>
       <c r="R14" t="n">
-        <v>7056713</v>
+        <v>7056595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>131566326</v>
       </c>
       <c r="B15" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131566299</v>
       </c>
       <c r="B16" t="n">
-        <v>83217</v>
+        <v>83223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>131566297</v>
       </c>
       <c r="B17" t="n">
-        <v>83100</v>
+        <v>83106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>131566312</v>
       </c>
       <c r="B18" t="n">
-        <v>79413</v>
+        <v>79419</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>131566302</v>
       </c>
       <c r="B19" t="n">
-        <v>83239</v>
+        <v>83245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131566315</v>
+        <v>131566322</v>
       </c>
       <c r="B20" t="n">
-        <v>80359</v>
+        <v>78272</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419594</v>
+        <v>419409</v>
       </c>
       <c r="R20" t="n">
-        <v>7056698</v>
+        <v>7056725</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>barken på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131566293</v>
+        <v>131566315</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>80365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419706</v>
+        <v>419594</v>
       </c>
       <c r="R21" t="n">
-        <v>7056590</v>
+        <v>7056698</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,6 +2882,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2898,10 +2913,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131566322</v>
+        <v>131566293</v>
       </c>
       <c r="B22" t="n">
-        <v>78266</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,21 +2924,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2933,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419409</v>
+        <v>419706</v>
       </c>
       <c r="R22" t="n">
-        <v>7056725</v>
+        <v>7056590</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,7 +2983,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2978,7 +2993,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,21 +3004,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3023,7 +3023,7 @@
         <v>131566313</v>
       </c>
       <c r="B23" t="n">
-        <v>79335</v>
+        <v>79341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,32 +3127,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131566307</v>
+        <v>131566323</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>92550</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419663</v>
+        <v>419357</v>
       </c>
       <c r="R24" t="n">
-        <v>7056675</v>
+        <v>7056778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131566323</v>
+        <v>131566304</v>
       </c>
       <c r="B25" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419357</v>
+        <v>419713</v>
       </c>
       <c r="R25" t="n">
-        <v>7056778</v>
+        <v>7056649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,32 +3341,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131566304</v>
+        <v>131566307</v>
       </c>
       <c r="B26" t="n">
-        <v>92544</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419713</v>
+        <v>419663</v>
       </c>
       <c r="R26" t="n">
-        <v>7056649</v>
+        <v>7056675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,7 +3451,7 @@
         <v>131566324</v>
       </c>
       <c r="B27" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>131566301</v>
       </c>
       <c r="B28" t="n">
-        <v>79413</v>
+        <v>79419</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131566306</v>
       </c>
       <c r="B29" t="n">
-        <v>79413</v>
+        <v>79419</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>131566294</v>
       </c>
       <c r="B30" t="n">
-        <v>83239</v>
+        <v>83245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>131566318</v>
       </c>
       <c r="B31" t="n">
-        <v>79413</v>
+        <v>79419</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>131584340</v>
       </c>
       <c r="B32" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>131584325</v>
       </c>
       <c r="B33" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>131584322</v>
       </c>
       <c r="B34" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>131584336</v>
       </c>
       <c r="B35" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>131584555</v>
       </c>
       <c r="B36" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>131584568</v>
       </c>
       <c r="B37" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>131584561</v>
       </c>
       <c r="B38" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>131584544</v>
       </c>
       <c r="B39" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>131584565</v>
       </c>
       <c r="B40" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>131584546</v>
       </c>
       <c r="B41" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>131584339</v>
       </c>
       <c r="B42" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>131584326</v>
       </c>
       <c r="B43" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>131584547</v>
       </c>
       <c r="B44" t="n">
-        <v>80395</v>
+        <v>80401</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>131584550</v>
       </c>
       <c r="B45" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>131584541</v>
       </c>
       <c r="B46" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>131584562</v>
       </c>
       <c r="B47" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>131584350</v>
       </c>
       <c r="B48" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>131584320</v>
       </c>
       <c r="B49" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131584571</v>
       </c>
       <c r="B50" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>131584563</v>
       </c>
       <c r="B51" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>131584328</v>
       </c>
       <c r="B52" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>131584321</v>
       </c>
       <c r="B53" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>131584567</v>
       </c>
       <c r="B54" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>131584558</v>
       </c>
       <c r="B55" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>131584323</v>
       </c>
       <c r="B56" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>131584556</v>
       </c>
       <c r="B57" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>131584569</v>
       </c>
       <c r="B58" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>131584334</v>
       </c>
       <c r="B59" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>131584327</v>
       </c>
       <c r="B60" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>131584560</v>
       </c>
       <c r="B61" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>131584337</v>
       </c>
       <c r="B62" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>131584324</v>
       </c>
       <c r="B63" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>131584331</v>
       </c>
       <c r="B64" t="n">
-        <v>92241</v>
+        <v>92247</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131584335</v>
       </c>
       <c r="B65" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>131584566</v>
       </c>
       <c r="B66" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>131584543</v>
       </c>
       <c r="B67" t="n">
-        <v>80388</v>
+        <v>80394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>131584554</v>
       </c>
       <c r="B68" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>131584542</v>
       </c>
       <c r="B69" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>131584329</v>
       </c>
       <c r="B70" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>131584333</v>
       </c>
       <c r="B71" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>131584319</v>
       </c>
       <c r="B72" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>131584553</v>
       </c>
       <c r="B73" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>131584347</v>
       </c>
       <c r="B74" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>131584338</v>
       </c>
       <c r="B75" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>131584332</v>
       </c>
       <c r="B76" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>131584314</v>
       </c>
       <c r="B77" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>131584545</v>
       </c>
       <c r="B78" t="n">
-        <v>80360</v>
+        <v>80366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>131584559</v>
       </c>
       <c r="B79" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>131584346</v>
       </c>
       <c r="B80" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>131584315</v>
       </c>
       <c r="B81" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>131584330</v>
       </c>
       <c r="B82" t="n">
-        <v>92241</v>
+        <v>92247</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>131584539</v>
       </c>
       <c r="B83" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131584557</v>
       </c>
       <c r="B84" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>131584538</v>
       </c>
       <c r="B85" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>131584317</v>
       </c>
       <c r="B86" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10262,6 +10262,129 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131652514</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58535</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skalet Västra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>418940</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7056963</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Äldre luckig bitvis flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -1890,32 +1890,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131566314</v>
+        <v>131566295</v>
       </c>
       <c r="B13" t="n">
-        <v>79419</v>
+        <v>83240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419597</v>
+        <v>419674</v>
       </c>
       <c r="R13" t="n">
-        <v>7056713</v>
+        <v>7056595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131566295</v>
+        <v>131566314</v>
       </c>
       <c r="B14" t="n">
-        <v>83240</v>
+        <v>79419</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419674</v>
+        <v>419597</v>
       </c>
       <c r="R14" t="n">
-        <v>7056595</v>
+        <v>7056713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131566322</v>
+        <v>131566315</v>
       </c>
       <c r="B20" t="n">
-        <v>78272</v>
+        <v>80365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419409</v>
+        <v>419594</v>
       </c>
       <c r="R20" t="n">
-        <v>7056725</v>
+        <v>7056698</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131566315</v>
+        <v>131566293</v>
       </c>
       <c r="B21" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,21 +2802,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419594</v>
+        <v>419706</v>
       </c>
       <c r="R21" t="n">
-        <v>7056698</v>
+        <v>7056590</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,21 +2882,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2913,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131566293</v>
+        <v>131566322</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>78272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,21 +2909,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2948,10 +2933,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419706</v>
+        <v>419409</v>
       </c>
       <c r="R22" t="n">
-        <v>7056590</v>
+        <v>7056725</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,7 +2968,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2993,7 +2978,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,6 +2989,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566308</v>
+        <v>131566303</v>
       </c>
       <c r="B5" t="n">
-        <v>92550</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419698</v>
+        <v>419713</v>
       </c>
       <c r="R5" t="n">
-        <v>7056652</v>
+        <v>7056649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566303</v>
+        <v>131566308</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>92550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419713</v>
+        <v>419698</v>
       </c>
       <c r="R6" t="n">
-        <v>7056649</v>
+        <v>7056652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,34 +1344,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131566316</v>
+        <v>131566311</v>
       </c>
       <c r="B8" t="n">
-        <v>80394</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419586</v>
+        <v>419593</v>
       </c>
       <c r="R8" t="n">
-        <v>7056712</v>
+        <v>7056723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,21 +1431,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1466,30 +1447,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131566311</v>
+        <v>131566316</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>80394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419593</v>
+        <v>419586</v>
       </c>
       <c r="R9" t="n">
-        <v>7056723</v>
+        <v>7056712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,6 +1538,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1890,32 +1890,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131566295</v>
+        <v>131566314</v>
       </c>
       <c r="B13" t="n">
-        <v>83240</v>
+        <v>79419</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419674</v>
+        <v>419597</v>
       </c>
       <c r="R13" t="n">
-        <v>7056595</v>
+        <v>7056713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131566314</v>
+        <v>131566295</v>
       </c>
       <c r="B14" t="n">
-        <v>79419</v>
+        <v>83240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419597</v>
+        <v>419674</v>
       </c>
       <c r="R14" t="n">
-        <v>7056713</v>
+        <v>7056595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566303</v>
+        <v>131566308</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419713</v>
+        <v>419698</v>
       </c>
       <c r="R5" t="n">
-        <v>7056649</v>
+        <v>7056652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566308</v>
+        <v>131566303</v>
       </c>
       <c r="B6" t="n">
-        <v>92550</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419698</v>
+        <v>419713</v>
       </c>
       <c r="R6" t="n">
-        <v>7056652</v>
+        <v>7056649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566308</v>
+        <v>131566303</v>
       </c>
       <c r="B5" t="n">
-        <v>92550</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419698</v>
+        <v>419713</v>
       </c>
       <c r="R5" t="n">
-        <v>7056652</v>
+        <v>7056649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566303</v>
+        <v>131566308</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>92551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419713</v>
+        <v>419698</v>
       </c>
       <c r="R6" t="n">
-        <v>7056649</v>
+        <v>7056652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,30 +1344,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131566311</v>
+        <v>131566316</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>80394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419593</v>
+        <v>419586</v>
       </c>
       <c r="R8" t="n">
-        <v>7056723</v>
+        <v>7056712</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,6 +1435,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1447,34 +1466,30 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131566316</v>
+        <v>131566311</v>
       </c>
       <c r="B9" t="n">
-        <v>80394</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419586</v>
+        <v>419593</v>
       </c>
       <c r="R9" t="n">
-        <v>7056712</v>
+        <v>7056723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,21 +1553,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3127,32 +3127,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131566323</v>
+        <v>131566307</v>
       </c>
       <c r="B24" t="n">
-        <v>92550</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419357</v>
+        <v>419663</v>
       </c>
       <c r="R24" t="n">
-        <v>7056778</v>
+        <v>7056675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,7 +3237,7 @@
         <v>131566304</v>
       </c>
       <c r="B25" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,32 +3341,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131566307</v>
+        <v>131566323</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>92551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419663</v>
+        <v>419357</v>
       </c>
       <c r="R26" t="n">
-        <v>7056675</v>
+        <v>7056778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -7712,7 +7712,7 @@
         <v>131584331</v>
       </c>
       <c r="B64" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>131584314</v>
       </c>
       <c r="B77" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>131584315</v>
       </c>
       <c r="B81" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>131584330</v>
       </c>
       <c r="B82" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>131584317</v>
       </c>
       <c r="B86" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>131566310</v>
       </c>
       <c r="B3" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131566305</v>
       </c>
       <c r="B4" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566303</v>
+        <v>131566308</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>92552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6459</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419713</v>
+        <v>419698</v>
       </c>
       <c r="R5" t="n">
-        <v>7056649</v>
+        <v>7056652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566308</v>
+        <v>131566303</v>
       </c>
       <c r="B6" t="n">
-        <v>92551</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6459</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419698</v>
+        <v>419713</v>
       </c>
       <c r="R6" t="n">
-        <v>7056652</v>
+        <v>7056649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
         <v>131566325</v>
       </c>
       <c r="B7" t="n">
-        <v>89213</v>
+        <v>89214</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,34 +1344,30 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131566316</v>
+        <v>131566311</v>
       </c>
       <c r="B8" t="n">
-        <v>80394</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419586</v>
+        <v>419593</v>
       </c>
       <c r="R8" t="n">
-        <v>7056712</v>
+        <v>7056723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,21 +1431,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1466,30 +1447,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131566311</v>
+        <v>131566316</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>80395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419593</v>
+        <v>419586</v>
       </c>
       <c r="R9" t="n">
-        <v>7056723</v>
+        <v>7056712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,6 +1538,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1572,7 +1572,7 @@
         <v>131566321</v>
       </c>
       <c r="B10" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131566319</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131566317</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>131566314</v>
       </c>
       <c r="B13" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>131566295</v>
       </c>
       <c r="B14" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>131566326</v>
       </c>
       <c r="B15" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131566299</v>
       </c>
       <c r="B16" t="n">
-        <v>83223</v>
+        <v>83224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131566297</v>
+        <v>131566312</v>
       </c>
       <c r="B17" t="n">
-        <v>83106</v>
+        <v>79420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419727</v>
+        <v>419590</v>
       </c>
       <c r="R17" t="n">
-        <v>7056633</v>
+        <v>7056714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,32 +2440,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131566312</v>
+        <v>131566297</v>
       </c>
       <c r="B18" t="n">
-        <v>79419</v>
+        <v>83107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419590</v>
+        <v>419727</v>
       </c>
       <c r="R18" t="n">
-        <v>7056714</v>
+        <v>7056633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,7 +2550,7 @@
         <v>131566302</v>
       </c>
       <c r="B19" t="n">
-        <v>83245</v>
+        <v>83246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>131566315</v>
       </c>
       <c r="B20" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>131566293</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>131566322</v>
       </c>
       <c r="B22" t="n">
-        <v>78272</v>
+        <v>78273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>131566313</v>
       </c>
       <c r="B23" t="n">
-        <v>79341</v>
+        <v>79342</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,32 +3127,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131566307</v>
+        <v>131566323</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>92552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419663</v>
+        <v>419357</v>
       </c>
       <c r="R24" t="n">
-        <v>7056675</v>
+        <v>7056778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,7 +3237,7 @@
         <v>131566304</v>
       </c>
       <c r="B25" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,32 +3341,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131566323</v>
+        <v>131566307</v>
       </c>
       <c r="B26" t="n">
-        <v>92551</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419357</v>
+        <v>419663</v>
       </c>
       <c r="R26" t="n">
-        <v>7056778</v>
+        <v>7056675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,7 +3451,7 @@
         <v>131566324</v>
       </c>
       <c r="B27" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>131566301</v>
       </c>
       <c r="B28" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131566306</v>
       </c>
       <c r="B29" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3765,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131566294</v>
+        <v>131566318</v>
       </c>
       <c r="B30" t="n">
-        <v>83245</v>
+        <v>79420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419680</v>
+        <v>419515</v>
       </c>
       <c r="R30" t="n">
-        <v>7056589</v>
+        <v>7056725</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,21 +3856,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>under rotben på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3887,32 +3872,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131566318</v>
+        <v>131566294</v>
       </c>
       <c r="B31" t="n">
-        <v>79419</v>
+        <v>83246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3922,10 +3907,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419515</v>
+        <v>419680</v>
       </c>
       <c r="R31" t="n">
-        <v>7056725</v>
+        <v>7056589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3957,7 +3942,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,7 +3952,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3978,6 +3963,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>under rotben på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3997,7 +3997,7 @@
         <v>131584340</v>
       </c>
       <c r="B32" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>131584325</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>131584322</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>131584336</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>131584555</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>131584568</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>131584561</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>131584544</v>
       </c>
       <c r="B39" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>131584565</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>131584546</v>
       </c>
       <c r="B41" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>131584339</v>
       </c>
       <c r="B42" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>131584326</v>
       </c>
       <c r="B43" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>131584547</v>
       </c>
       <c r="B44" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>131584550</v>
       </c>
       <c r="B45" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>131584541</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>131584562</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>131584350</v>
       </c>
       <c r="B48" t="n">
-        <v>89213</v>
+        <v>89214</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>131584320</v>
       </c>
       <c r="B49" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131584571</v>
       </c>
       <c r="B50" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>131584563</v>
       </c>
       <c r="B51" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>131584328</v>
       </c>
       <c r="B52" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>131584321</v>
       </c>
       <c r="B53" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>131584567</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>131584558</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>131584323</v>
       </c>
       <c r="B56" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>131584556</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>131584569</v>
       </c>
       <c r="B58" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>131584334</v>
       </c>
       <c r="B59" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>131584327</v>
       </c>
       <c r="B60" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>131584560</v>
       </c>
       <c r="B61" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>131584337</v>
       </c>
       <c r="B62" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>131584324</v>
       </c>
       <c r="B63" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>131584331</v>
       </c>
       <c r="B64" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131584335</v>
       </c>
       <c r="B65" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>131584566</v>
       </c>
       <c r="B66" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>131584543</v>
       </c>
       <c r="B67" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>131584554</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>131584542</v>
       </c>
       <c r="B69" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>131584329</v>
       </c>
       <c r="B70" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>131584333</v>
       </c>
       <c r="B71" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>131584319</v>
       </c>
       <c r="B72" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>131584553</v>
       </c>
       <c r="B73" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>131584347</v>
       </c>
       <c r="B74" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>131584338</v>
       </c>
       <c r="B75" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>131584332</v>
       </c>
       <c r="B76" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>131584314</v>
       </c>
       <c r="B77" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>131584545</v>
       </c>
       <c r="B78" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>131584559</v>
       </c>
       <c r="B79" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>131584346</v>
       </c>
       <c r="B80" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>131584315</v>
       </c>
       <c r="B81" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>131584330</v>
       </c>
       <c r="B82" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>131584539</v>
       </c>
       <c r="B83" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131584557</v>
       </c>
       <c r="B84" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>131584538</v>
       </c>
       <c r="B85" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>131584317</v>
       </c>
       <c r="B86" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>131652514</v>
       </c>
       <c r="B87" t="n">
-        <v>58535</v>
+        <v>58536</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>131566310</v>
       </c>
       <c r="B3" t="n">
-        <v>79420</v>
+        <v>79423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>131566305</v>
       </c>
       <c r="B4" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>131566308</v>
       </c>
       <c r="B5" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>131566303</v>
       </c>
       <c r="B6" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>131566325</v>
       </c>
       <c r="B7" t="n">
-        <v>89214</v>
+        <v>89217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>131566311</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131566316</v>
       </c>
       <c r="B9" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>131566321</v>
       </c>
       <c r="B10" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>131566319</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131566317</v>
       </c>
       <c r="B12" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131566314</v>
+        <v>131566295</v>
       </c>
       <c r="B13" t="n">
-        <v>79420</v>
+        <v>83244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419597</v>
+        <v>419674</v>
       </c>
       <c r="R13" t="n">
-        <v>7056713</v>
+        <v>7056595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131566295</v>
+        <v>131566314</v>
       </c>
       <c r="B14" t="n">
-        <v>83241</v>
+        <v>79423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419674</v>
+        <v>419597</v>
       </c>
       <c r="R14" t="n">
-        <v>7056595</v>
+        <v>7056713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>131566326</v>
       </c>
       <c r="B15" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>131566299</v>
       </c>
       <c r="B16" t="n">
-        <v>83224</v>
+        <v>83227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131566312</v>
+        <v>131566297</v>
       </c>
       <c r="B17" t="n">
-        <v>79420</v>
+        <v>83110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419590</v>
+        <v>419727</v>
       </c>
       <c r="R17" t="n">
-        <v>7056714</v>
+        <v>7056633</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,32 +2440,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131566297</v>
+        <v>131566312</v>
       </c>
       <c r="B18" t="n">
-        <v>83107</v>
+        <v>79423</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419727</v>
+        <v>419590</v>
       </c>
       <c r="R18" t="n">
-        <v>7056633</v>
+        <v>7056714</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,7 +2550,7 @@
         <v>131566302</v>
       </c>
       <c r="B19" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>131566315</v>
       </c>
       <c r="B20" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>131566293</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>131566322</v>
       </c>
       <c r="B22" t="n">
-        <v>78273</v>
+        <v>78276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>131566313</v>
       </c>
       <c r="B23" t="n">
-        <v>79342</v>
+        <v>79345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,32 +3127,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131566323</v>
+        <v>131566307</v>
       </c>
       <c r="B24" t="n">
-        <v>92552</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419357</v>
+        <v>419663</v>
       </c>
       <c r="R24" t="n">
-        <v>7056778</v>
+        <v>7056675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,7 +3237,7 @@
         <v>131566304</v>
       </c>
       <c r="B25" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,32 +3341,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131566307</v>
+        <v>131566323</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>92555</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419663</v>
+        <v>419357</v>
       </c>
       <c r="R26" t="n">
-        <v>7056675</v>
+        <v>7056778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,7 +3451,7 @@
         <v>131566324</v>
       </c>
       <c r="B27" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>131566301</v>
       </c>
       <c r="B28" t="n">
-        <v>79420</v>
+        <v>79423</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>131566306</v>
       </c>
       <c r="B29" t="n">
-        <v>79420</v>
+        <v>79423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3765,32 +3765,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131566318</v>
+        <v>131566294</v>
       </c>
       <c r="B30" t="n">
-        <v>79420</v>
+        <v>83249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419515</v>
+        <v>419680</v>
       </c>
       <c r="R30" t="n">
-        <v>7056725</v>
+        <v>7056589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,6 +3856,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>under rotben på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3872,32 +3887,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131566294</v>
+        <v>131566318</v>
       </c>
       <c r="B31" t="n">
-        <v>83246</v>
+        <v>79423</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3907,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419680</v>
+        <v>419515</v>
       </c>
       <c r="R31" t="n">
-        <v>7056589</v>
+        <v>7056725</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3952,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,21 +3978,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>under rotben på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3997,7 +3997,7 @@
         <v>131584340</v>
       </c>
       <c r="B32" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>131584325</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>131584322</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>131584336</v>
       </c>
       <c r="B35" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>131584555</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>131584568</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>131584561</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>131584544</v>
       </c>
       <c r="B39" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>131584565</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>131584546</v>
       </c>
       <c r="B41" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>131584339</v>
       </c>
       <c r="B42" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>131584326</v>
       </c>
       <c r="B43" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>131584547</v>
       </c>
       <c r="B44" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>131584550</v>
       </c>
       <c r="B45" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>131584541</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>131584562</v>
       </c>
       <c r="B47" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>131584350</v>
       </c>
       <c r="B48" t="n">
-        <v>89214</v>
+        <v>89217</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>131584320</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131584571</v>
       </c>
       <c r="B50" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>131584563</v>
       </c>
       <c r="B51" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>131584328</v>
       </c>
       <c r="B52" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>131584321</v>
       </c>
       <c r="B53" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>131584567</v>
       </c>
       <c r="B54" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>131584558</v>
       </c>
       <c r="B55" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>131584323</v>
       </c>
       <c r="B56" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>131584556</v>
       </c>
       <c r="B57" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>131584569</v>
       </c>
       <c r="B58" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>131584334</v>
       </c>
       <c r="B59" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>131584327</v>
       </c>
       <c r="B60" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>131584560</v>
       </c>
       <c r="B61" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>131584337</v>
       </c>
       <c r="B62" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>131584324</v>
       </c>
       <c r="B63" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>131584331</v>
       </c>
       <c r="B64" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131584335</v>
       </c>
       <c r="B65" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>131584566</v>
       </c>
       <c r="B66" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>131584543</v>
       </c>
       <c r="B67" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>131584554</v>
       </c>
       <c r="B68" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>131584542</v>
       </c>
       <c r="B69" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>131584329</v>
       </c>
       <c r="B70" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>131584333</v>
       </c>
       <c r="B71" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>131584319</v>
       </c>
       <c r="B72" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>131584553</v>
       </c>
       <c r="B73" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>131584347</v>
       </c>
       <c r="B74" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>131584338</v>
       </c>
       <c r="B75" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>131584332</v>
       </c>
       <c r="B76" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>131584314</v>
       </c>
       <c r="B77" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>131584545</v>
       </c>
       <c r="B78" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>131584559</v>
       </c>
       <c r="B79" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>131584346</v>
       </c>
       <c r="B80" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>131584315</v>
       </c>
       <c r="B81" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>131584330</v>
       </c>
       <c r="B82" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>131584539</v>
       </c>
       <c r="B83" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131584557</v>
       </c>
       <c r="B84" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>131584538</v>
       </c>
       <c r="B85" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>131584317</v>
       </c>
       <c r="B86" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>131652514</v>
       </c>
       <c r="B87" t="n">
-        <v>58536</v>
+        <v>58539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>165076</v>
+        <v>131566313</v>
       </c>
       <c r="B2" t="n">
-        <v>85702</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gråvalen, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418969.1834778364</v>
+        <v>419603</v>
       </c>
       <c r="R2" t="n">
-        <v>7056957.860061476</v>
+        <v>7056711</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-08-18</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-08-18</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,86 +766,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddare</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131566310</v>
+        <v>165076</v>
       </c>
       <c r="B3" t="n">
-        <v>79435</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419633</v>
+        <v>418969</v>
       </c>
       <c r="R3" t="n">
-        <v>7056685</v>
+        <v>7056958</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2008-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2008-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,48 +863,70 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131566305</v>
+        <v>131566325</v>
       </c>
       <c r="B4" t="n">
-        <v>75254</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419714</v>
+        <v>419367</v>
       </c>
       <c r="R4" t="n">
-        <v>7056648</v>
+        <v>7056739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131566308</v>
+        <v>131584350</v>
       </c>
       <c r="B5" t="n">
-        <v>92571</v>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419698</v>
+        <v>419731</v>
       </c>
       <c r="R5" t="n">
-        <v>7056652</v>
+        <v>7056563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,57 +1093,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131566303</v>
+        <v>131584574</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>89354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419713</v>
+        <v>418857</v>
       </c>
       <c r="R6" t="n">
-        <v>7056649</v>
+        <v>7056944</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,22 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,50 +1191,81 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal luckig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131566325</v>
+        <v>131566291</v>
       </c>
       <c r="B7" t="n">
-        <v>89233</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419367</v>
+        <v>419677</v>
       </c>
       <c r="R7" t="n">
-        <v>7056739</v>
+        <v>7056578</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131566316</v>
+        <v>131566301</v>
       </c>
       <c r="B8" t="n">
-        <v>80410</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419586</v>
+        <v>419715</v>
       </c>
       <c r="R8" t="n">
-        <v>7056712</v>
+        <v>7056651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,21 +1438,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1466,30 +1454,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131566311</v>
+        <v>131566306</v>
       </c>
       <c r="B9" t="n">
-        <v>91868</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419593</v>
+        <v>419655</v>
       </c>
       <c r="R9" t="n">
-        <v>7056723</v>
+        <v>7056675</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,32 +1561,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131566321</v>
+        <v>131566310</v>
       </c>
       <c r="B10" t="n">
-        <v>83256</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419413</v>
+        <v>419633</v>
       </c>
       <c r="R10" t="n">
-        <v>7056727</v>
+        <v>7056685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131566319</v>
+        <v>131566312</v>
       </c>
       <c r="B11" t="n">
-        <v>79276</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419473</v>
+        <v>419590</v>
       </c>
       <c r="R11" t="n">
-        <v>7056721</v>
+        <v>7056714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,32 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131566317</v>
+        <v>131566314</v>
       </c>
       <c r="B12" t="n">
-        <v>80381</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1818,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419510</v>
+        <v>419597</v>
       </c>
       <c r="R12" t="n">
-        <v>7056746</v>
+        <v>7056713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,32 +1882,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131566295</v>
+        <v>131566318</v>
       </c>
       <c r="B13" t="n">
-        <v>83256</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419674</v>
+        <v>419515</v>
       </c>
       <c r="R13" t="n">
-        <v>7056595</v>
+        <v>7056725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131566314</v>
+        <v>131566297</v>
       </c>
       <c r="B14" t="n">
-        <v>79435</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419597</v>
+        <v>419727</v>
       </c>
       <c r="R14" t="n">
-        <v>7056713</v>
+        <v>7056633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131566326</v>
+        <v>131566294</v>
       </c>
       <c r="B15" t="n">
-        <v>80341</v>
+        <v>83363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419407</v>
+        <v>419680</v>
       </c>
       <c r="R15" t="n">
-        <v>7056625</v>
+        <v>7056589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,17 +2190,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>under rotben på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2226,32 +2218,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131566299</v>
+        <v>131566302</v>
       </c>
       <c r="B16" t="n">
-        <v>83239</v>
+        <v>83363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419733</v>
+        <v>419713</v>
       </c>
       <c r="R16" t="n">
-        <v>7056597</v>
+        <v>7056649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,6 +2309,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>under rotben på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2333,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131566297</v>
+        <v>131584544</v>
       </c>
       <c r="B17" t="n">
-        <v>83122</v>
+        <v>80489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,34 +2351,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419727</v>
+        <v>419333</v>
       </c>
       <c r="R17" t="n">
-        <v>7056633</v>
+        <v>7056680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,22 +2412,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,28 +2426,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131566302</v>
+        <v>131584545</v>
       </c>
       <c r="B18" t="n">
-        <v>83261</v>
+        <v>80489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,34 +2481,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419713</v>
+        <v>419306</v>
       </c>
       <c r="R18" t="n">
-        <v>7056649</v>
+        <v>7056720</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,22 +2538,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,78 +2552,92 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>under rotben på gammal gran # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131566312</v>
+        <v>131584546</v>
       </c>
       <c r="B19" t="n">
-        <v>79435</v>
+        <v>80489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419590</v>
+        <v>419073</v>
       </c>
       <c r="R19" t="n">
-        <v>7056714</v>
+        <v>7056773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,22 +2664,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,50 +2683,76 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131566322</v>
+        <v>131566304</v>
       </c>
       <c r="B20" t="n">
-        <v>78288</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2762,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419409</v>
+        <v>419713</v>
       </c>
       <c r="R20" t="n">
-        <v>7056725</v>
+        <v>7056649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,21 +2818,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2791,32 +2834,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131566315</v>
+        <v>131566308</v>
       </c>
       <c r="B21" t="n">
-        <v>80381</v>
+        <v>92199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2869,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419594</v>
+        <v>419698</v>
       </c>
       <c r="R21" t="n">
-        <v>7056698</v>
+        <v>7056652</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2914,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,21 +2925,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2913,32 +2941,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131566293</v>
+        <v>131566323</v>
       </c>
       <c r="B22" t="n">
-        <v>79276</v>
+        <v>92199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2948,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419706</v>
+        <v>419357</v>
       </c>
       <c r="R22" t="n">
-        <v>7056590</v>
+        <v>7056778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2993,7 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,32 +3048,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131566313</v>
+        <v>131584314</v>
       </c>
       <c r="B23" t="n">
-        <v>79357</v>
+        <v>92199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3055,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419603</v>
+        <v>419729</v>
       </c>
       <c r="R23" t="n">
-        <v>7056711</v>
+        <v>7056657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3085,22 +3113,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,22 +3133,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131566304</v>
+        <v>131584315</v>
       </c>
       <c r="B24" t="n">
-        <v>92571</v>
+        <v>92199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,10 +3180,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419713</v>
+        <v>419707</v>
       </c>
       <c r="R24" t="n">
-        <v>7056649</v>
+        <v>7056665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,22 +3210,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,22 +3230,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131566323</v>
+        <v>131584317</v>
       </c>
       <c r="B25" t="n">
-        <v>92571</v>
+        <v>92199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,10 +3277,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419357</v>
+        <v>419081</v>
       </c>
       <c r="R25" t="n">
-        <v>7056778</v>
+        <v>7056790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3299,22 +3307,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3329,26 +3327,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131566307</v>
+        <v>131566293</v>
       </c>
       <c r="B26" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3376,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419663</v>
+        <v>419706</v>
       </c>
       <c r="R26" t="n">
-        <v>7056675</v>
+        <v>7056590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3411,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3421,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,30 +3446,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131566324</v>
+        <v>131566307</v>
       </c>
       <c r="B27" t="n">
-        <v>91868</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3479,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419354</v>
+        <v>419663</v>
       </c>
       <c r="R27" t="n">
-        <v>7056785</v>
+        <v>7056675</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,10 +3553,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131566301</v>
+        <v>131566319</v>
       </c>
       <c r="B28" t="n">
-        <v>79435</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,21 +3564,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3586,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419715</v>
+        <v>419473</v>
       </c>
       <c r="R28" t="n">
-        <v>7056651</v>
+        <v>7056721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3621,7 +3623,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3631,7 +3633,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3658,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131566318</v>
+        <v>131584346</v>
       </c>
       <c r="B29" t="n">
-        <v>79435</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,21 +3671,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3693,10 +3695,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419515</v>
+        <v>418537</v>
       </c>
       <c r="R29" t="n">
-        <v>7056725</v>
+        <v>7057018</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3723,22 +3725,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,22 +3750,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131566306</v>
+        <v>131584347</v>
       </c>
       <c r="B30" t="n">
-        <v>79435</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,21 +3773,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3797,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419655</v>
+        <v>418505</v>
       </c>
       <c r="R30" t="n">
-        <v>7056675</v>
+        <v>7057056</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3830,22 +3827,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,57 +3852,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131566294</v>
+        <v>131584553</v>
       </c>
       <c r="B31" t="n">
-        <v>83261</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419680</v>
+        <v>419469</v>
       </c>
       <c r="R31" t="n">
-        <v>7056589</v>
+        <v>7056553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,22 +3932,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3961,9 +3946,15 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3976,59 +3967,66 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>under rotben på gammal gran # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131584340</v>
+        <v>131584554</v>
       </c>
       <c r="B32" t="n">
-        <v>91868</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>418697</v>
+        <v>419395</v>
       </c>
       <c r="R32" t="n">
-        <v>7056879</v>
+        <v>7056573</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4063,69 +4061,103 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131584325</v>
+        <v>131584555</v>
       </c>
       <c r="B33" t="n">
-        <v>57914</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>418928</v>
+        <v>419343</v>
       </c>
       <c r="R33" t="n">
-        <v>7056947</v>
+        <v>7056648</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4162,7 +4194,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en ca 6 meter hög granhögstubbe.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4171,71 +4203,92 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131584322</v>
+        <v>131584556</v>
       </c>
       <c r="B34" t="n">
-        <v>57914</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419747</v>
+        <v>419342</v>
       </c>
       <c r="R34" t="n">
-        <v>7056615</v>
+        <v>7056685</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,7 +4325,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Bohål ca 3,3 m upp i grantickerötad granhögstubbe</t>
+          <t>På en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4281,59 +4334,92 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131584336</v>
+        <v>131584557</v>
       </c>
       <c r="B35" t="n">
-        <v>91868</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>419047</v>
+        <v>419261</v>
       </c>
       <c r="R35" t="n">
-        <v>7056875</v>
+        <v>7056756</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4368,38 +4454,69 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131584555</v>
+        <v>131584558</v>
       </c>
       <c r="B36" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4430,10 +4547,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419343</v>
+        <v>419228</v>
       </c>
       <c r="R36" t="n">
-        <v>7056648</v>
+        <v>7056767</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,11 +4585,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På en ca 6 meter hög granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4500,12 +4612,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4523,14 +4635,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131584568</v>
+        <v>131584559</v>
       </c>
       <c r="B37" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4561,10 +4673,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>418619</v>
+        <v>419132</v>
       </c>
       <c r="R37" t="n">
-        <v>7056987</v>
+        <v>7056815</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4599,11 +4711,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4621,12 +4728,12 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -4636,7 +4743,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4654,14 +4761,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131584561</v>
+        <v>131584560</v>
       </c>
       <c r="B38" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4692,10 +4799,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419013</v>
+        <v>419058</v>
       </c>
       <c r="R38" t="n">
-        <v>7056860</v>
+        <v>7056809</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4730,11 +4837,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4762,12 +4864,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4785,41 +4887,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131584544</v>
+        <v>131584561</v>
       </c>
       <c r="B39" t="n">
-        <v>80382</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4827,10 +4925,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419333</v>
+        <v>419013</v>
       </c>
       <c r="R39" t="n">
-        <v>7056680</v>
+        <v>7056860</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4865,6 +4963,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4882,22 +4985,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4915,14 +5018,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131584565</v>
+        <v>131584562</v>
       </c>
       <c r="B40" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4953,10 +5056,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>418773</v>
+        <v>418989</v>
       </c>
       <c r="R40" t="n">
-        <v>7056981</v>
+        <v>7056899</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5016,14 +5119,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5041,32 +5139,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131584546</v>
+        <v>131584563</v>
       </c>
       <c r="B41" t="n">
-        <v>80382</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5079,10 +5177,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419073</v>
+        <v>418925</v>
       </c>
       <c r="R41" t="n">
-        <v>7056773</v>
+        <v>7056918</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5119,7 +5217,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>På stående död gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5139,22 +5237,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5172,41 +5270,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131584339</v>
+        <v>131584564</v>
       </c>
       <c r="B42" t="n">
-        <v>91868</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>418677</v>
+        <v>418864</v>
       </c>
       <c r="R42" t="n">
-        <v>7056893</v>
+        <v>7056953</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5247,79 +5352,87 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131584326</v>
+        <v>131584565</v>
       </c>
       <c r="B43" t="n">
-        <v>57914</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>418619</v>
+        <v>418773</v>
       </c>
       <c r="R43" t="n">
-        <v>7056989</v>
+        <v>7056981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5354,70 +5467,87 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Observerades hackandes på både gran och björk</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131584547</v>
+        <v>131584566</v>
       </c>
       <c r="B44" t="n">
-        <v>80417</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5425,10 +5555,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419307</v>
+        <v>418673</v>
       </c>
       <c r="R44" t="n">
-        <v>7056721</v>
+        <v>7056906</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5463,6 +5593,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På stående död gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5480,22 +5615,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5513,37 +5648,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131584550</v>
+        <v>131584567</v>
       </c>
       <c r="B45" t="n">
-        <v>91868</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5551,10 +5686,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419077</v>
+        <v>418672</v>
       </c>
       <c r="R45" t="n">
-        <v>7056784</v>
+        <v>7056939</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5591,7 +5726,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående levande grov gran.</t>
+          <t>Rikligt på en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5621,12 +5756,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5644,42 +5779,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131584541</v>
+        <v>131584568</v>
       </c>
       <c r="B46" t="n">
-        <v>57914</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5687,10 +5817,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>418507</v>
+        <v>418619</v>
       </c>
       <c r="R46" t="n">
-        <v>7057041</v>
+        <v>7056987</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5727,7 +5857,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal grov gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5736,6 +5866,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5746,22 +5877,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5779,14 +5910,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131584562</v>
+        <v>131584569</v>
       </c>
       <c r="B47" t="n">
-        <v>79276</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5817,10 +5948,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>418989</v>
+        <v>418566</v>
       </c>
       <c r="R47" t="n">
-        <v>7056899</v>
+        <v>7057014</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5855,6 +5986,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt med garnlav på flera granar.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5880,9 +6016,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5900,45 +6041,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131584350</v>
+        <v>131584571</v>
       </c>
       <c r="B48" t="n">
-        <v>89233</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419731</v>
+        <v>418510</v>
       </c>
       <c r="R48" t="n">
-        <v>7056563</v>
+        <v>7057043</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5973,56 +6117,87 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växer här på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131584320</v>
+        <v>131566305</v>
       </c>
       <c r="B49" t="n">
-        <v>57914</v>
+        <v>75340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6032,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419749</v>
+        <v>419714</v>
       </c>
       <c r="R49" t="n">
-        <v>7056588</v>
+        <v>7056648</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6062,17 +6237,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6087,60 +6267,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131584571</v>
+        <v>131566299</v>
       </c>
       <c r="B50" t="n">
-        <v>79276</v>
+        <v>83341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>418510</v>
+        <v>419733</v>
       </c>
       <c r="R50" t="n">
-        <v>7057043</v>
+        <v>7056597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6167,17 +6344,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Växer här på en gammal gran.</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6186,54 +6368,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131584563</v>
+        <v>131566295</v>
       </c>
       <c r="B51" t="n">
-        <v>79276</v>
+        <v>83358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6241,37 +6397,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>418925</v>
+        <v>419674</v>
       </c>
       <c r="R51" t="n">
-        <v>7056918</v>
+        <v>7056595</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6298,17 +6451,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På stående död gran.</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6317,54 +6475,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131584328</v>
+        <v>131566321</v>
       </c>
       <c r="B52" t="n">
-        <v>58073</v>
+        <v>83358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6372,46 +6504,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419750</v>
+        <v>419413</v>
       </c>
       <c r="R52" t="n">
-        <v>7056612</v>
+        <v>7056727</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6438,12 +6558,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6458,22 +6588,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131584321</v>
+        <v>131566315</v>
       </c>
       <c r="B53" t="n">
-        <v>57914</v>
+        <v>80488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,21 +6611,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6505,10 +6635,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419741</v>
+        <v>419594</v>
       </c>
       <c r="R53" t="n">
-        <v>7056603</v>
+        <v>7056698</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6535,17 +6665,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6556,26 +6691,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131584567</v>
+        <v>131566317</v>
       </c>
       <c r="B54" t="n">
-        <v>79276</v>
+        <v>80488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6583,37 +6733,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>418672</v>
+        <v>419510</v>
       </c>
       <c r="R54" t="n">
-        <v>7056939</v>
+        <v>7056746</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6640,17 +6787,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt på en stående död gran med full längd.</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6659,92 +6811,63 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131584558</v>
+        <v>131566303</v>
       </c>
       <c r="B55" t="n">
-        <v>79276</v>
+        <v>79629</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419228</v>
+        <v>419713</v>
       </c>
       <c r="R55" t="n">
-        <v>7056767</v>
+        <v>7056649</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6771,12 +6894,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,76 +6918,50 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131584323</v>
+        <v>131566316</v>
       </c>
       <c r="B56" t="n">
-        <v>57914</v>
+        <v>80493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6864,10 +6971,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419542</v>
+        <v>419586</v>
       </c>
       <c r="R56" t="n">
-        <v>7056682</v>
+        <v>7056712</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6894,17 +7001,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6915,53 +7027,72 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131584556</v>
+        <v>131584543</v>
       </c>
       <c r="B57" t="n">
-        <v>79276</v>
+        <v>80493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6969,10 +7100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419342</v>
+        <v>419307</v>
       </c>
       <c r="R57" t="n">
-        <v>7056685</v>
+        <v>7056720</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7007,11 +7138,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7029,22 +7155,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7062,37 +7188,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131584569</v>
+        <v>131584547</v>
       </c>
       <c r="B58" t="n">
-        <v>79276</v>
+        <v>80500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7100,10 +7230,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>418566</v>
+        <v>419307</v>
       </c>
       <c r="R58" t="n">
-        <v>7057014</v>
+        <v>7056721</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7138,11 +7268,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt med garnlav på flera granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7160,22 +7285,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7193,30 +7318,34 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131584334</v>
+        <v>131584329</v>
       </c>
       <c r="B59" t="n">
-        <v>91868</v>
+        <v>57972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7224,10 +7353,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419494</v>
+        <v>418697</v>
       </c>
       <c r="R59" t="n">
-        <v>7056656</v>
+        <v>7056879</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7260,6 +7389,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7286,10 +7420,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131584327</v>
+        <v>131584319</v>
       </c>
       <c r="B60" t="n">
-        <v>57914</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7321,10 +7455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>418610</v>
+        <v>419476</v>
       </c>
       <c r="R60" t="n">
-        <v>7056996</v>
+        <v>7056575</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7361,7 +7495,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7388,10 +7522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131584560</v>
+        <v>131584320</v>
       </c>
       <c r="B61" t="n">
-        <v>79276</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7399,37 +7533,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419058</v>
+        <v>419749</v>
       </c>
       <c r="R61" t="n">
-        <v>7056809</v>
+        <v>7056588</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7464,60 +7595,39 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131584337</v>
+        <v>131584321</v>
       </c>
       <c r="B62" t="n">
-        <v>91868</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7525,19 +7635,23 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7545,10 +7659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419005</v>
+        <v>419741</v>
       </c>
       <c r="R62" t="n">
-        <v>7056915</v>
+        <v>7056603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7581,6 +7695,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7607,10 +7726,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131584324</v>
+        <v>131584322</v>
       </c>
       <c r="B63" t="n">
-        <v>57914</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,16 +7755,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419365</v>
+        <v>419747</v>
       </c>
       <c r="R63" t="n">
-        <v>7056680</v>
+        <v>7056615</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7682,7 +7809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål ca 3,3 m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7709,10 +7836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131584331</v>
+        <v>131584323</v>
       </c>
       <c r="B64" t="n">
-        <v>92268</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7720,21 +7847,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7744,10 +7871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419500</v>
+        <v>419542</v>
       </c>
       <c r="R64" t="n">
-        <v>7056661</v>
+        <v>7056682</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7782,13 +7909,17 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7807,10 +7938,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131584335</v>
+        <v>131584324</v>
       </c>
       <c r="B65" t="n">
-        <v>91868</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7818,19 +7949,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7838,10 +7973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419501</v>
+        <v>419365</v>
       </c>
       <c r="R65" t="n">
-        <v>7056663</v>
+        <v>7056680</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7874,6 +8009,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7900,10 +8040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131584566</v>
+        <v>131584325</v>
       </c>
       <c r="B66" t="n">
-        <v>79276</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7911,37 +8051,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>418673</v>
+        <v>418928</v>
       </c>
       <c r="R66" t="n">
-        <v>7056906</v>
+        <v>7056947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7978,7 +8115,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På stående död gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7987,96 +8124,79 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131584543</v>
+        <v>131584326</v>
       </c>
       <c r="B67" t="n">
-        <v>80410</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419307</v>
+        <v>418619</v>
       </c>
       <c r="R67" t="n">
-        <v>7056720</v>
+        <v>7056989</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,60 +8231,39 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Observerades hackandes på både gran och björk</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131584554</v>
+        <v>131584327</v>
       </c>
       <c r="B68" t="n">
-        <v>79276</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8172,37 +8271,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419395</v>
+        <v>418610</v>
       </c>
       <c r="R68" t="n">
-        <v>7056573</v>
+        <v>7056996</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8239,7 +8335,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8248,54 +8344,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131584542</v>
+        <v>131584538</v>
       </c>
       <c r="B69" t="n">
-        <v>58073</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8303,50 +8373,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>418940</v>
+        <v>419244</v>
       </c>
       <c r="R69" t="n">
-        <v>7056963</v>
+        <v>7056755</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8383,7 +8445,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal bitvis flerskiktad och luckig granskog med murkna björkhögstubbar för talltitans bohål.</t>
+          <t>Ringhack, äldre, på en stående döende gran med full längd och 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8398,6 +8460,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8415,10 +8497,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131584329</v>
+        <v>131584539</v>
       </c>
       <c r="B70" t="n">
-        <v>57911</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8426,16 +8508,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8444,16 +8526,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>418697</v>
+        <v>419098</v>
       </c>
       <c r="R70" t="n">
-        <v>7056879</v>
+        <v>7056781</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8490,7 +8580,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8501,26 +8591,51 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131584333</v>
+        <v>131584541</v>
       </c>
       <c r="B71" t="n">
-        <v>91868</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,30 +8643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419555</v>
+        <v>418507</v>
       </c>
       <c r="R71" t="n">
-        <v>7056651</v>
+        <v>7057041</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8586,6 +8713,11 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal grov gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8594,43 +8726,68 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131584319</v>
+        <v>131652514</v>
       </c>
       <c r="B72" t="n">
-        <v>57914</v>
+        <v>58614</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8638,17 +8795,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419476</v>
+        <v>418940</v>
       </c>
       <c r="R72" t="n">
-        <v>7056575</v>
+        <v>7056963</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8683,11 +8856,6 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8696,26 +8864,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Äldre luckig bitvis flerskiktad granskog.</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131584553</v>
+        <v>131584328</v>
       </c>
       <c r="B73" t="n">
-        <v>79276</v>
+        <v>58136</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8723,37 +8901,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419469</v>
+        <v>419750</v>
       </c>
       <c r="R73" t="n">
-        <v>7056553</v>
+        <v>7056612</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8794,49 +8981,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131584347</v>
+        <v>131584542</v>
       </c>
       <c r="B74" t="n">
-        <v>79276</v>
+        <v>58136</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8844,34 +9010,50 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skalet, Jmt</t>
+          <t>Skalet Västra, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>418505</v>
+        <v>418940</v>
       </c>
       <c r="R74" t="n">
-        <v>7057056</v>
+        <v>7056963</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8908,7 +9090,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Fyndplatsen finns i gammal bitvis flerskiktad och luckig granskog med murkna björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8919,26 +9101,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131584338</v>
+        <v>131566296</v>
       </c>
       <c r="B75" t="n">
-        <v>91868</v>
+        <v>78382</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8946,19 +9133,23 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8966,10 +9157,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>418936</v>
+        <v>419680</v>
       </c>
       <c r="R75" t="n">
-        <v>7056928</v>
+        <v>7056580</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8996,12 +9187,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9012,26 +9213,41 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>på barken av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131584332</v>
+        <v>131566322</v>
       </c>
       <c r="B76" t="n">
-        <v>91868</v>
+        <v>78382</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9039,19 +9255,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9059,10 +9279,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419747</v>
+        <v>419409</v>
       </c>
       <c r="R76" t="n">
-        <v>7056611</v>
+        <v>7056725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9089,12 +9309,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9105,26 +9335,41 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131584314</v>
+        <v>131566326</v>
       </c>
       <c r="B77" t="n">
-        <v>92571</v>
+        <v>80438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9132,21 +9377,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9156,10 +9401,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419729</v>
+        <v>419407</v>
       </c>
       <c r="R77" t="n">
-        <v>7056657</v>
+        <v>7056625</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9186,12 +9431,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9202,26 +9457,41 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131584545</v>
+        <v>131584330</v>
       </c>
       <c r="B78" t="n">
-        <v>80382</v>
+        <v>92366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9229,37 +9499,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6040186</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419306</v>
+        <v>418867</v>
       </c>
       <c r="R78" t="n">
-        <v>7056720</v>
+        <v>7056983</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9304,50 +9571,25 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131584559</v>
+        <v>131584331</v>
       </c>
       <c r="B79" t="n">
-        <v>79276</v>
+        <v>92366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9355,37 +9597,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Skalet Västra, Jmt</t>
+          <t>Skalet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419132</v>
+        <v>419500</v>
       </c>
       <c r="R79" t="n">
-        <v>7056815</v>
+        <v>7056661</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9430,961 +9669,18 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>131584346</v>
-      </c>
-      <c r="B80" t="n">
-        <v>79276</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Skalet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>418537</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7057018</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>131584315</v>
-      </c>
-      <c r="B81" t="n">
-        <v>92571</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Skalet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>419707</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7056665</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>131584330</v>
-      </c>
-      <c r="B82" t="n">
-        <v>92268</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Skalet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>418867</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7056983</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>131584539</v>
-      </c>
-      <c r="B83" t="n">
-        <v>57914</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Skalet Västra, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>419098</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7056781</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>131584557</v>
-      </c>
-      <c r="B84" t="n">
-        <v>79276</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Skalet Västra, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>419261</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7056756</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>131584538</v>
-      </c>
-      <c r="B85" t="n">
-        <v>57914</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Skalet Västra, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>419244</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7056755</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående döende gran med full längd och 41 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>131584317</v>
-      </c>
-      <c r="B86" t="n">
-        <v>92571</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Skalet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>419081</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7056790</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>131652514</v>
-      </c>
-      <c r="B87" t="n">
-        <v>58585</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>102125</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Pinicola enucleator</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Skalet Västra, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>418940</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7056963</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Äldre luckig bitvis flerskiktad granskog.</t>
-        </is>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6244-2026 artfynd.xlsx
+++ b/artfynd/A 6244-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/165076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566291</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566301</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566306</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566310</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566312</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566314</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566318</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566297</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566302</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2467,6 +2547,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584544</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2593,6 +2678,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584545</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584546</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2831,6 +2926,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566304</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2938,6 +3038,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566308</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3045,6 +3150,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566323</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3142,6 +3252,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584314</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3239,6 +3354,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584315</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584317</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3443,6 +3568,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566293</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3550,6 +3680,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566307</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3657,6 +3792,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566319</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3759,6 +3899,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584346</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3861,6 +4006,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584347</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3982,6 +4132,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584553</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4113,6 +4268,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584554</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4244,6 +4404,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584555</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4375,6 +4540,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584556</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4506,6 +4676,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584557</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4632,6 +4807,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584558</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4758,6 +4938,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584559</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4884,6 +5069,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584560</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5015,6 +5205,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584561</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5136,6 +5331,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584562</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5267,6 +5467,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584563</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5388,6 +5593,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584564</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5514,6 +5724,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584565</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5645,6 +5860,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584566</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5776,6 +5996,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584567</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5907,6 +6132,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584568</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6038,6 +6268,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584569</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6169,6 +6404,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584571</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6276,6 +6516,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566305</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6383,6 +6628,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566299</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6490,6 +6740,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566295</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6597,6 +6852,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566321</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6719,6 +6979,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566315</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6826,6 +7091,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566317</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6933,6 +7203,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566303</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7055,6 +7330,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566316</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7185,6 +7465,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584543</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7315,6 +7600,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584547</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7417,6 +7707,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584329</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7519,6 +7814,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584319</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7621,6 +7921,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584320</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7723,6 +8028,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584321</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7833,6 +8143,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584322</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7935,6 +8250,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584323</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8037,6 +8357,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584324</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8139,6 +8464,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584325</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8257,6 +8587,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584326</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8359,6 +8694,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584327</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8494,6 +8834,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584538</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8629,6 +8974,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584539</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8764,6 +9114,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584541</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8887,6 +9242,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131652514</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8996,6 +9356,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584328</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9119,6 +9484,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584542</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9241,6 +9611,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566296</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9363,6 +9738,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566322</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9485,6 +9865,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131566326</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9583,6 +9968,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584330</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9681,8 +10071,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>